--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7685185185185185</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C2">
-        <v>0.7323943661971831</v>
+        <v>0.7676056338028169</v>
       </c>
       <c r="D2">
-        <v>0.3140495867768595</v>
+        <v>0.2920353982300885</v>
       </c>
       <c r="E2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
